--- a/dossier-cfa/livrables/Analytique_CFA_WEFORM.xlsx
+++ b/dossier-cfa/livrables/Analytique_CFA_WEFORM.xlsx
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>20415.52</v>
+        <v>20264.8</v>
       </c>
     </row>
     <row r="23">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>2766.5</v>
+        <v>2917.22</v>
       </c>
     </row>
     <row r="24">
@@ -1487,7 +1487,7 @@
         <v>31136.14</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -15701,16 +15701,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
@@ -16842,16 +16842,197 @@
       </c>
       <c r="D48" s="12" t="inlineStr"/>
     </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Notre lecture \ votre modèle</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Directe</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Indirecte</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Non incorporable</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Produit</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>(non renseignée)</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Directe</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>-90058.72</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>-29878.04</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>-9700</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>-93.72</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>-67449.38</v>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>-197179.86</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Indirecte — répartie par clé</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>-4378.97</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>-13702.08</v>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>-198</v>
+      </c>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n">
+        <v>-153706.01</v>
+      </c>
+      <c r="G52" s="9" t="n">
+        <v>-171985.06</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Indirecte — commun pur</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>-6418.5</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>-71873.67999999999</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>-814.62</v>
+      </c>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n">
+        <v>-26888.21</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>-105995.01</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Hors périmètre</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n">
+        <v>-65.48999999999999</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>-5301.6</v>
+      </c>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n">
+        <v>-5367.09</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Produit</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n">
+        <v>312571.11</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>198592.05</v>
+      </c>
+      <c r="G55" s="9" t="n">
+        <v>511663.16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="n">
+        <v>-100356.19</v>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>-115519.29</v>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>-16014.22</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>312477.39</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>-49451.55</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>31136.14</v>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>Votre classeur porte sa propre colonne « Nature ». Elle ne dit pas la même chose que la nôtre, et c'est normal : la vôtre est une déclaration poste par poste, la nôtre se déduit des clés effectivement appliquées à chaque ligne. La diagonale est l'accord. Les 169 lignes que nous lisons « directes » et que vous déclarez « indirectes » sont des charges dont la pièce désigne une activité mais que votre modèle range en structure ; les 51 lignes en sens inverse passent par le commun malgré votre déclaration. Les 319 lignes « non renseignée » sont celles que votre modèle ne porte pas — il est bâti sur le relevé, le grand livre sur les droits constatés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>Une charge « directe » porte 100 % sur une seule activité — apprentissage, formation continue ou Ligue AURA — parce que sa pièce la désigne. Une charge « indirecte » passe en tout ou partie par le commun, et c'est la cascade des clés qui la répartit ensuite. Le taux indirect par compte se lit dans la dernière colonne.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A49:I49"/>
+  <mergeCells count="2">
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A59:I59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17426,10 +17607,10 @@
         <v>-1273.49</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>-9531.799999999999</v>
+        <v>-9682.52</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>-2015.57</v>
+        <v>-1864.85</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>-405.75</v>
@@ -18148,10 +18329,10 @@
         <v>-263122.76</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>-44772.99</v>
+        <v>-44923.71</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>-9420.690000000001</v>
+        <v>-9269.969999999999</v>
       </c>
       <c r="G43" s="13" t="n">
         <v>-156411.08</v>
@@ -18175,10 +18356,10 @@
         <v>145469.56</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>24753.55</v>
+        <v>24602.83</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>15179.31</v>
+        <v>15330.03</v>
       </c>
       <c r="G45" s="13" t="n">
         <v>-156411.08</v>
@@ -18298,16 +18479,16 @@
         <v>69526.53999999999</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>-44772.99</v>
+        <v>-44923.71</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>24753.55</v>
+        <v>24602.83</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>-4338.03</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>20415.52</v>
+        <v>20264.8</v>
       </c>
     </row>
     <row r="7">
@@ -18320,16 +18501,16 @@
         <v>24600</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>-9420.690000000001</v>
+        <v>-9269.969999999999</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>15179.31</v>
+        <v>15330.03</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>-12412.81</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>2766.5</v>
+        <v>2917.22</v>
       </c>
     </row>
     <row r="8">
@@ -62007,17 +62188,17 @@
       </c>
       <c r="I689" s="4" t="inlineStr">
         <is>
-          <t>arbitrage nominatif</t>
+          <t>FPC</t>
         </is>
       </c>
       <c r="J689" s="9" t="n">
         <v>-0</v>
       </c>
       <c r="K689" s="9" t="n">
-        <v>-602.88</v>
+        <v>-753.6</v>
       </c>
       <c r="L689" s="9" t="n">
-        <v>-150.72</v>
+        <v>-0</v>
       </c>
       <c r="M689" s="9" t="n">
         <v>-0</v>
@@ -62027,7 +62208,7 @@
       </c>
       <c r="O689" s="4" t="inlineStr">
         <is>
-          <t>modèle WE-FORM (ligne appariée)</t>
+          <t>motif du relevé bancaire</t>
         </is>
       </c>
     </row>
@@ -82320,10 +82501,10 @@
         <v>145469.56</v>
       </c>
       <c r="K1011" s="13" t="n">
-        <v>24753.55</v>
+        <v>24602.83</v>
       </c>
       <c r="L1011" s="13" t="n">
-        <v>15179.31</v>
+        <v>15330.03</v>
       </c>
       <c r="M1011" s="13" t="n">
         <v>-156411.08</v>
@@ -82770,10 +82951,10 @@
         <v>69526.53999999999</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-49111.02</v>
+        <v>-49261.74</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>20415.52</v>
+        <v>20264.8</v>
       </c>
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr"/>
@@ -82798,10 +82979,10 @@
         <v>24600</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>-21833.5</v>
+        <v>-21682.78</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>2766.5</v>
+        <v>2917.22</v>
       </c>
       <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr"/>
@@ -87111,10 +87292,10 @@
         <v>-380.4</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>-6916.68</v>
+        <v>-7067.4</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>-1705.68</v>
+        <v>-1554.96</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>-31.89</v>
@@ -87279,10 +87460,10 @@
         <v>-17774.67</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>-22410.78</v>
+        <v>-22561.5</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>-2470.74</v>
+        <v>-2320.02</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>-11846.72</v>
